--- a/Old scripts/LCOH_AN_2019.xlsx
+++ b/Old scripts/LCOH_AN_2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20396"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20400"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Natural gas vs. green chemicals\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Fossil vs. green chemicals\Old scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4236B6DA-9873-4533-A435-6089463039C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6967E111-FA15-497F-ADFA-D0580DCE6EEE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,7 +1142,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1179,7 +1179,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
